--- a/terminology/ValueSet-AllergenWithExceptions.xlsx
+++ b/terminology/ValueSet-AllergenWithExceptions.xlsx
@@ -34,7 +34,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -115,7 +115,7 @@
     <t>ValueSet URL</t>
   </si>
   <si>
-    <t>https://ncez.mzcr.cz/terminology/ValueSet/eHDSIAllergenNoDrug-cz</t>
+    <t>https://ncez.mzcr.cz/terminology/ValueSet/eHDSIAllergenNoDrug</t>
   </si>
   <si>
     <t>https://sukl.cz/terminology/ValueSet/dlp-lecivepripravky</t>
@@ -124,10 +124,10 @@
     <t>https://sukl.cz/terminology/ValueSet/dlp-atc</t>
   </si>
   <si>
-    <t>https://ncez.mzcr.cz/terminology/ValueSet/eHDSIAbsentOrUnknownAllergy-cz</t>
-  </si>
-  <si>
-    <t>https://ncez.mzcr.cz/terminology/ValueSet/eHDSIExceptionalValue-cz</t>
+    <t>https://ncez.mzcr.cz/terminology/ValueSet/eHDSIAbsentOrUnknownAllergy</t>
+  </si>
+  <si>
+    <t>https://ncez.mzcr.cz/terminology/ValueSet/eHDSIExceptionalValue</t>
   </si>
 </sst>
 </file>
